--- a/data-raw/benchmarks_2025.xlsx
+++ b/data-raw/benchmarks_2025.xlsx
@@ -1,89 +1,84 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taylorgrant/R/bmw/brand_tracker_v2/extra_analysis/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E709F89-E5C3-0541-8815-CD3D62C5B2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="21440" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="overall" sheetId="1" r:id="rId1"/>
-    <sheet name="women" sheetId="2" r:id="rId2"/>
-    <sheet name="aapi" sheetId="3" r:id="rId3"/>
-    <sheet name="genz_mill" sheetId="4" r:id="rId4"/>
+    <sheet name="overall" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="women" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="aapi" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="genz_mill" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="millennials" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="gen_z" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="18">
-  <si>
-    <t>statement</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Social</t>
-  </si>
-  <si>
-    <t>Ad change opinion of BMW (T2B Better)</t>
-  </si>
-  <si>
-    <t>Ad change purchase consideration (T2B More Likely)</t>
-  </si>
-  <si>
-    <t>Fits the way I feel about the brand</t>
-  </si>
-  <si>
-    <t>I was emotionally moved by the ad</t>
-  </si>
-  <si>
-    <t>Is believable</t>
-  </si>
-  <si>
-    <t>Is confusing</t>
-  </si>
-  <si>
-    <t>Is enjoyable</t>
-  </si>
-  <si>
-    <t>Is irritating</t>
-  </si>
-  <si>
-    <t>Is relevant to me</t>
-  </si>
-  <si>
-    <t>Is unique and different</t>
-  </si>
-  <si>
-    <t>Makes me think about the brand in a new way</t>
-  </si>
-  <si>
-    <t>Makes me think this is a brand I identify with</t>
-  </si>
-  <si>
-    <t>Makes me think this is a brand for me</t>
-  </si>
-  <si>
-    <t>Makes me want to learn more about the product/brand</t>
-  </si>
-  <si>
-    <t>Seen ad past 2 weeks</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t xml:space="preserve">statement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ad change opinion of BMW (T2B Better)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ad change purchase consideration (T2B More Likely)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fits the way I feel about the brand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was emotionally moved by the ad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is believable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is confusing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is enjoyable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is irritating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is relevant to me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is unique and different</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makes me think about the brand in a new way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makes me think this is a brand I identify with</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makes me think this is a brand for me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makes me want to learn more about the product/brand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seen ad past 2 weeks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -119,15 +114,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -409,14 +395,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="42.5" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -427,186 +410,183 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>0.702118540289003</v>
       </c>
-      <c r="C2">
-        <v>0.66291618828932297</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C2" t="n">
+        <v>0.662916188289323</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>0.70168993387215295</v>
-      </c>
-      <c r="C3">
-        <v>0.67210103329506299</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B3" t="n">
+        <v>0.701689933872153</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.672101033295063</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>0.73922361009061999</v>
-      </c>
-      <c r="C4">
-        <v>0.67876004592422501</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B4" t="n">
+        <v>0.73922361009062</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.678760045924225</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>0.49534655890276802</v>
-      </c>
-      <c r="C5">
-        <v>0.47715269804822003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B5" t="n">
+        <v>0.495346558902768</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.47715269804822</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <v>0.82812882684300804</v>
-      </c>
-      <c r="C6">
-        <v>0.79517795637198596</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B6" t="n">
+        <v>0.828128826843008</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.795177956371986</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>0.17346313984815101</v>
-      </c>
-      <c r="C7">
-        <v>0.19517795637198601</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B7" t="n">
+        <v>0.173463139848151</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.195177956371986</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
-        <v>0.78655400440852297</v>
-      </c>
-      <c r="C8">
-        <v>0.75407577497129696</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B8" t="n">
+        <v>0.786554004408523</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.754075774971297</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
-        <v>0.20162870438403099</v>
-      </c>
-      <c r="C9">
+      <c r="B9" t="n">
+        <v>0.201628704384031</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.235591274397245</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
-        <v>0.68723977467548403</v>
-      </c>
-      <c r="C10">
-        <v>0.67508610792192902</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B10" t="n">
+        <v>0.687239774675484</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.675086107921929</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11">
-        <v>0.70609845701689899</v>
-      </c>
-      <c r="C11">
-        <v>0.70241102181400705</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" t="n">
+        <v>0.706098457016899</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.702411021814007</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12">
-        <v>0.66807494489346098</v>
-      </c>
-      <c r="C12">
+      <c r="B12" t="n">
+        <v>0.668074944893461</v>
+      </c>
+      <c r="C12" t="n">
         <v>0.647761194029851</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>0.67591231937301</v>
       </c>
-      <c r="C13">
-        <v>0.65258323765786497</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C13" t="n">
+        <v>0.652583237657865</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B14">
-        <v>0.67150379622826395</v>
-      </c>
-      <c r="C14">
-        <v>0.63995407577497099</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B14" t="n">
+        <v>0.671503796228264</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.639954075774971</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B15">
-        <v>0.69385255939260304</v>
-      </c>
-      <c r="C15">
-        <v>0.66429391504018398</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B15" t="n">
+        <v>0.693852559392603</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.664293915040184</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>0.317229977957384</v>
       </c>
-      <c r="C16">
-        <v>0.25970149253731301</v>
+      <c r="C16" t="n">
+        <v>0.259701492537313</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="45.1640625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -617,186 +597,183 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>0.63929121725731897</v>
-      </c>
-      <c r="C2">
-        <v>0.59231651376146799</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2" t="n">
+        <v>0.639291217257319</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.592316513761468</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>0.63158705701078599</v>
-      </c>
-      <c r="C3">
-        <v>0.60321100917431203</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B3" t="n">
+        <v>0.631587057010786</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.603211009174312</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>0.70693374422188004</v>
-      </c>
-      <c r="C4">
-        <v>0.63073394495412805</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B4" t="n">
+        <v>0.70693374422188</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.630733944954128</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>0.41448382126348199</v>
-      </c>
-      <c r="C5">
-        <v>0.41055045871559598</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B5" t="n">
+        <v>0.414483821263482</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.410550458715596</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <v>0.81140215716486896</v>
-      </c>
-      <c r="C6">
-        <v>0.78497706422018398</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B6" t="n">
+        <v>0.811402157164869</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.784977064220184</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>0.145916795069337</v>
       </c>
-      <c r="C7">
-        <v>0.16513761467889901</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C7" t="n">
+        <v>0.165137614678899</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
-        <v>0.76610169491525404</v>
-      </c>
-      <c r="C8">
-        <v>0.73967889908256901</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B8" t="n">
+        <v>0.766101694915254</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.739678899082569</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>0.155161787365177</v>
       </c>
-      <c r="C9">
-        <v>0.18864678899082599</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C9" t="n">
+        <v>0.188646788990826</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>0.636671802773498</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>0.630160550458716</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11">
-        <v>0.66224961479198796</v>
-      </c>
-      <c r="C11">
-        <v>0.67947247706421998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" t="n">
+        <v>0.662249614791988</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.67947247706422</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12">
-        <v>0.61895223420647105</v>
-      </c>
-      <c r="C12">
-        <v>0.60034403669724801</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B12" t="n">
+        <v>0.618952234206471</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.600344036697248</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13">
-        <v>0.62804314329737998</v>
-      </c>
-      <c r="C13">
-        <v>0.61238532110091703</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B13" t="n">
+        <v>0.62804314329738</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.612385321100917</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B14">
-        <v>0.61941448382126396</v>
-      </c>
-      <c r="C14">
-        <v>0.58600917431192701</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B14" t="n">
+        <v>0.619414483821264</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.586009174311927</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B15">
-        <v>0.64838212634822801</v>
-      </c>
-      <c r="C15">
-        <v>0.61811926605504597</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B15" t="n">
+        <v>0.648382126348228</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.618119266055046</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B16">
-        <v>0.23281972265023099</v>
-      </c>
-      <c r="C16">
-        <v>0.19094036697247699</v>
+      <c r="B16" t="n">
+        <v>0.232819722650231</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.190940366972477</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="43" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -807,186 +784,183 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>0.67152466367713004</v>
-      </c>
-      <c r="C2">
-        <v>0.58959537572254295</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2" t="n">
+        <v>0.67152466367713</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.589595375722543</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>0.63565022421524697</v>
-      </c>
-      <c r="C3">
-        <v>0.58381502890173398</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B3" t="n">
+        <v>0.635650224215247</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.583815028901734</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>0.69843049327354301</v>
-      </c>
-      <c r="C4">
-        <v>0.58959537572254295</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B4" t="n">
+        <v>0.698430493273543</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.589595375722543</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>0.42825112107623298</v>
-      </c>
-      <c r="C5">
-        <v>0.41618497109826602</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B5" t="n">
+        <v>0.428251121076233</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.416184971098266</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <v>0.79932735426009005</v>
-      </c>
-      <c r="C6">
-        <v>0.75144508670520205</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B6" t="n">
+        <v>0.79932735426009</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.751445086705202</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>0.123318385650224</v>
       </c>
-      <c r="C7">
-        <v>0.15606936416184999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C7" t="n">
+        <v>0.15606936416185</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
-        <v>0.73542600896860999</v>
-      </c>
-      <c r="C8">
-        <v>0.65895953757225401</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B8" t="n">
+        <v>0.73542600896861</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.658959537572254</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
-        <v>0.13004484304932701</v>
-      </c>
-      <c r="C9">
-        <v>0.17341040462427701</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B9" t="n">
+        <v>0.130044843049327</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.173410404624277</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
-        <v>0.65134529147982101</v>
-      </c>
-      <c r="C10">
-        <v>0.56647398843930596</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B10" t="n">
+        <v>0.651345291479821</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.566473988439306</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11">
-        <v>0.64013452914798197</v>
-      </c>
-      <c r="C11">
-        <v>0.58959537572254295</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" t="n">
+        <v>0.640134529147982</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.589595375722543</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12">
-        <v>0.60762331838564998</v>
-      </c>
-      <c r="C12">
-        <v>0.60115606936416199</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B12" t="n">
+        <v>0.60762331838565</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.601156069364162</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13">
-        <v>0.62556053811659196</v>
-      </c>
-      <c r="C13">
-        <v>0.56647398843930596</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B13" t="n">
+        <v>0.625560538116592</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.566473988439306</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B14">
-        <v>0.62443946188340804</v>
-      </c>
-      <c r="C14">
-        <v>0.54913294797687895</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B14" t="n">
+        <v>0.624439461883408</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.549132947976879</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B15">
-        <v>0.64686098654708502</v>
-      </c>
-      <c r="C15">
-        <v>0.57225433526011604</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B15" t="n">
+        <v>0.646860986547085</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.572254335260116</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B16">
-        <v>0.19506726457399101</v>
-      </c>
-      <c r="C16">
+      <c r="B16" t="n">
+        <v>0.195067264573991</v>
+      </c>
+      <c r="C16" t="n">
         <v>0.184971098265896</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="45.5" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -997,173 +971,547 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>0.795920546774883</v>
       </c>
-      <c r="C2">
-        <v>0.75501432664756496</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C2" t="n">
+        <v>0.755014326647565</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>0.80371636052968798</v>
-      </c>
-      <c r="C3">
-        <v>0.76683381088825198</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B3" t="n">
+        <v>0.803716360529688</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.766833810888252</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>0.79805638615976104</v>
-      </c>
-      <c r="C4">
+      <c r="B4" t="n">
+        <v>0.798056386159761</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.736389684813754</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>0.59045279794959404</v>
-      </c>
-      <c r="C5">
-        <v>0.55766475644699098</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B5" t="n">
+        <v>0.590452797949594</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.557664756446991</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <v>0.85444254592054703</v>
-      </c>
-      <c r="C6">
-        <v>0.83202005730659001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B6" t="n">
+        <v>0.854442545920547</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.83202005730659</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>0.213797522426314</v>
       </c>
-      <c r="C7">
-        <v>0.21597421203438399</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C7" t="n">
+        <v>0.215974212034384</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
-        <v>0.83169585647159305</v>
-      </c>
-      <c r="C8">
+      <c r="B8" t="n">
+        <v>0.831695856471593</v>
+      </c>
+      <c r="C8" t="n">
         <v>0.805873925501433</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>0.243378897906877</v>
       </c>
-      <c r="C9">
-        <v>0.24928366762177701</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C9" t="n">
+        <v>0.249283667621777</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
-        <v>0.76794105083297703</v>
-      </c>
-      <c r="C10">
-        <v>0.75214899713466998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B10" t="n">
+        <v>0.767941050832977</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.75214899713467</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11">
-        <v>0.76217428449380598</v>
-      </c>
-      <c r="C11">
-        <v>0.75644699140401195</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" t="n">
+        <v>0.762174284493806</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.756446991404012</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12">
-        <v>0.73729175565997396</v>
-      </c>
-      <c r="C12">
-        <v>0.71812320916905403</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B12" t="n">
+        <v>0.737291755659974</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.718123209169054</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13">
-        <v>0.75224263135412195</v>
-      </c>
-      <c r="C13">
-        <v>0.72636103151862497</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B13" t="n">
+        <v>0.752242631354122</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.726361031518625</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B14">
-        <v>0.75277659120034202</v>
-      </c>
-      <c r="C14">
-        <v>0.71561604584527205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B14" t="n">
+        <v>0.752776591200342</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.715616045845272</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B15">
-        <v>0.77018368218709998</v>
-      </c>
-      <c r="C15">
-        <v>0.73961318051575897</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B15" t="n">
+        <v>0.7701836821871</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.739613180515759</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B16">
-        <v>0.39513028620247798</v>
-      </c>
-      <c r="C16">
-        <v>0.33022922636103202</v>
+      <c r="B16" t="n">
+        <v>0.395130286202478</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.330229226361032</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.796969696969697</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.753903040262942</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.805575757575758</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.758422350041085</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.803151515151515</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7341824157765</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.59769696969697</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.559161873459326</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.85830303030303</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.835250616269515</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.210545454545455</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.213229252259655</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.836969696969697</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.811421528348398</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.242060606060606</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.248562037797864</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.772242424242424</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.752670501232539</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.766060606060606</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.76253081347576</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.742545454545455</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.719802793755136</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.730484798685292</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.756242424242424</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.721446179129006</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.773818181818182</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.741166803615448</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.393575757575758</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.318405916187346</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.788150807899461</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.762569832402235</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.789946140035907</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.824022346368715</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.76032315978456</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.751396648044693</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.536804308797127</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.547486033519553</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.825852782764811</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.810055865921788</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.237881508078995</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.23463687150838</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.792639138240575</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.768156424581006</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.253141831238779</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.254189944134078</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.736086175942549</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.748603351955307</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.733393177737881</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.715083798882682</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.698384201077199</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.706703910614525</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.724416517055655</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.698324022346369</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.727109515260323</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.675977653631285</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.74326750448833</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.729050279329609</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.406642728904847</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.410614525139665</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/data-raw/benchmarks_2025.xlsx
+++ b/data-raw/benchmarks_2025.xlsx
@@ -12,6 +12,7 @@
     <sheet name="genz_mill" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="millennials" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="gen_z" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ev_intender" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -1514,4 +1515,191 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.823567393058918</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.778994845360825</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.844390637610977</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.802835051546392</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.842776432606941</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.769329896907217</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.618079096045198</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.577319587628866</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.895560936238902</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.846649484536082</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.163841807909605</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.179768041237113</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.864245359160613</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.826675257731959</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.193543179983858</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.219072164948454</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.823567393058918</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.790592783505155</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.801291364003228</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.769974226804124</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.786763518966909</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.751288659793814</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.804196933010492</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.76159793814433</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.802582728006457</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.751288659793814</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.810653753026634</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.766752577319588</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.359967715899919</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.298969072164948</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>